--- a/output/ATI_buyout_client_unserviceable.xlsx
+++ b/output/ATI_buyout_client_unserviceable.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Лист2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист2'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист2'!$A$1:$G$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -994,23 +994,23 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>930-6201-001</t>
+          <t>2612311-1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CONTROL UNIT-WEATHER RADAR</t>
+          <t>WHEEL ASSY - MLG</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1019,29 +1019,29 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>S800-3000-00</t>
+          <t>930-6201-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RECORDER, FLIGHT DATA</t>
+          <t>CONTROL UNIT-WEATHER RADAR</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1056,18 +1056,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>27600-3</t>
+          <t>S800-3000-00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VALVE ASSY</t>
+          <t>RECORDER, FLIGHT DATA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1087,18 +1087,18 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2LA006178-02</t>
+          <t>27600-3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>FLOODLIGHT UNIT-FIRST OFFICER</t>
+          <t>VALVE ASSY</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1118,36 +1118,67 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>854D100-24</t>
+          <t>2LA006178-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>FLOODLIGHT UNIT-FIRST OFFICER</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>CRJ200</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>854D100-24</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>CRJ200</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>